--- a/projecten/2_vrije_opdracht/raw_data/relatieve_prevalentie_vergelijking.xlsx
+++ b/projecten/2_vrije_opdracht/raw_data/relatieve_prevalentie_vergelijking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rache\Documents\dsfb2\dsfb2_workflows_portfolio\dsfb2_workflows_portfolio\projecten\2_vrije_opdracht\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C304B53-348E-4F87-A58C-DDD2ACEB8162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84692F94-F3AC-4A38-B4EB-EDD44A6C157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4B780E1E-B963-4C4A-96C8-63764AC9D28D}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{4B780E1E-B963-4C4A-96C8-63764AC9D28D}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
